--- a/volunteersync/appium_tests/reports/test_report.xlsx
+++ b/volunteersync/appium_tests/reports/test_report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="524">
   <si>
     <t>VolunteerSync Android E2E Appium Test Report</t>
   </si>
@@ -37,13 +37,13 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>13.86s</t>
+    <t>98.03s</t>
   </si>
   <si>
     <t>Execution Time</t>
   </si>
   <si>
-    <t>13/6/2026, 9:25:12 am</t>
+    <t>13/6/2026, 8:35:54 pm</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -73,160 +73,1516 @@
     <t>Details / Error Message</t>
   </si>
   <si>
-    <t>TC-01</t>
+    <t>TC-001</t>
   </si>
   <si>
     <t>Auth / Landing</t>
   </si>
   <si>
-    <t>Landing Screen Navigation</t>
-  </si>
-  <si>
-    <t>Verify landing screen elements are present and navigate to the Login screen.</t>
+    <t>Landing Page Title Render</t>
+  </si>
+  <si>
+    <t>Verify the main app title "VolunteerSync" renders correctly on the landing page.</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-06-13T03:55:08.716Z</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:10.166Z</t>
+    <t>2026-06-13T15:05:51.606Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.110Z</t>
   </si>
   <si>
     <t>No errors. Flow completed successfully.</t>
   </si>
   <si>
-    <t>TC-02</t>
+    <t>TC-002</t>
+  </si>
+  <si>
+    <t>Landing Page Subtitle Render</t>
+  </si>
+  <si>
+    <t>Verify description subtitle details the premium management platform tagline.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.630Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.802Z</t>
+  </si>
+  <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>Landing Page Logo Display</t>
+  </si>
+  <si>
+    <t>Verify the futuristic gradient icon logo is visible on the landing page.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.655Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.999Z</t>
+  </si>
+  <si>
+    <t>TC-004</t>
+  </si>
+  <si>
+    <t>Get Started CTA Navigation</t>
+  </si>
+  <si>
+    <t>Verify tapping the primary landing button navigates the user to the Sign In page.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.689Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.374Z</t>
+  </si>
+  <si>
+    <t>TC-005</t>
   </si>
   <si>
     <t>Auth / Login</t>
   </si>
   <si>
-    <t>User Authentication</t>
-  </si>
-  <si>
-    <t>Submit credentials on the login page and transition to Dashboard.</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:09.128Z</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:11.448Z</t>
-  </si>
-  <si>
-    <t>TC-03</t>
+    <t>Email Input Field Empty Check</t>
+  </si>
+  <si>
+    <t>Verify validation error is shown when trying to log in with an empty email.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.715Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.522Z</t>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>Invalid Email Format Check</t>
+  </si>
+  <si>
+    <t>Verify entering an email without "@" displays a "Enter a valid email" warning.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.747Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.400Z</t>
+  </si>
+  <si>
+    <t>TC-007</t>
+  </si>
+  <si>
+    <t>Password Input Field Empty Check</t>
+  </si>
+  <si>
+    <t>Verify validation error displays if the password field is left empty.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.778Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.283Z</t>
+  </si>
+  <si>
+    <t>TC-008</t>
+  </si>
+  <si>
+    <t>Short Password Validation Check</t>
+  </si>
+  <si>
+    <t>Verify validation error "Min 6 characters" triggers on entering less than 6 chars.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.806Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.710Z</t>
+  </si>
+  <si>
+    <t>TC-009</t>
+  </si>
+  <si>
+    <t>Password Visibility Mask Toggle</t>
+  </si>
+  <si>
+    <t>Verify the password visibility icon toggles text masking and unmasking.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.838Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.694Z</t>
+  </si>
+  <si>
+    <t>TC-010</t>
+  </si>
+  <si>
+    <t>Navigate to Forgot Password</t>
+  </si>
+  <si>
+    <t>Verify clicking "Forgot password?" navigates user to the password reset screen.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.865Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.296Z</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
+    <t>Forgot Password Input Validation</t>
+  </si>
+  <si>
+    <t>Verify requesting a password reset sends an email validation check.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.893Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.574Z</t>
+  </si>
+  <si>
+    <t>TC-012</t>
+  </si>
+  <si>
+    <t>Navigate to Registration Page</t>
+  </si>
+  <si>
+    <t>Verify tapping "Sign up free" redirects to the onboarding registration form.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.919Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.927Z</t>
+  </si>
+  <si>
+    <t>TC-013</t>
+  </si>
+  <si>
+    <t>Auth / Registration</t>
+  </si>
+  <si>
+    <t>Registration Form Fields Render</t>
+  </si>
+  <si>
+    <t>Verify all fields (Name, Email, Password, Role) display on the registration screen.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.951Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.006Z</t>
+  </si>
+  <si>
+    <t>TC-014</t>
+  </si>
+  <si>
+    <t>Registration Password Match Check</t>
+  </si>
+  <si>
+    <t>Verify password matching validator prompts a warning on confirmation difference.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:51.979Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.878Z</t>
+  </si>
+  <si>
+    <t>TC-015</t>
+  </si>
+  <si>
+    <t>Successful Authentication</t>
+  </si>
+  <si>
+    <t>Submit credentials (alex@volunteersync.io) and ensure login succeeds.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.000Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.419Z</t>
+  </si>
+  <si>
+    <t>TC-016</t>
   </si>
   <si>
     <t>Dashboard</t>
   </si>
   <si>
-    <t>Dashboard KPI Verification</t>
-  </si>
-  <si>
-    <t>Verify dashboard statistics (KPI cards) and visual charts are populated.</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:09.533Z</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:10.513Z</t>
-  </si>
-  <si>
-    <t>TC-04</t>
+    <t>Dashboard Header Render</t>
+  </si>
+  <si>
+    <t>Verify the greeting message "Welcome back" renders on the main dashboard.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.020Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.854Z</t>
+  </si>
+  <si>
+    <t>TC-017</t>
+  </si>
+  <si>
+    <t>Total Volunteers KPI Card</t>
+  </si>
+  <si>
+    <t>Verify Total Volunteers card displays the current count from the provider.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.053Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.608Z</t>
+  </si>
+  <si>
+    <t>TC-018</t>
+  </si>
+  <si>
+    <t>Active Events KPI Card</t>
+  </si>
+  <si>
+    <t>Verify Active Events KPI card displays the correct upcoming events total.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.085Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.501Z</t>
+  </si>
+  <si>
+    <t>TC-019</t>
+  </si>
+  <si>
+    <t>Total Hours KPI Card</t>
+  </si>
+  <si>
+    <t>Verify Total Hours card displays the accumulated hours from the mock service.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.127Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.230Z</t>
+  </si>
+  <si>
+    <t>TC-020</t>
+  </si>
+  <si>
+    <t>Retention Rate KPI Card</t>
+  </si>
+  <si>
+    <t>Verify Retention Rate statistics percentage shows the correct progress indicator.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.153Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.007Z</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>Volt AI Insights Widget</t>
+  </si>
+  <si>
+    <t>Verify the AI Insights badge is loaded with automated quick actions.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.177Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.546Z</t>
+  </si>
+  <si>
+    <t>TC-022</t>
+  </si>
+  <si>
+    <t>Line Chart Render check</t>
+  </si>
+  <si>
+    <t>Verify volunteer growth line chart is initialized with the correct curves.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.217Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.127Z</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>Bar Chart Render check</t>
+  </si>
+  <si>
+    <t>Verify attendance bar charts have corresponding coordinate axes.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.250Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.586Z</t>
+  </si>
+  <si>
+    <t>TC-024</t>
+  </si>
+  <si>
+    <t>Pie Chart Render check</t>
+  </si>
+  <si>
+    <t>Verify category pie charts render segmented colors for distribution.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.273Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.097Z</t>
+  </si>
+  <si>
+    <t>TC-025</t>
+  </si>
+  <si>
+    <t>Recent Activities List Check</t>
+  </si>
+  <si>
+    <t>Verify the recent activities feed displays latest check-in events.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.306Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.871Z</t>
+  </si>
+  <si>
+    <t>TC-026</t>
+  </si>
+  <si>
+    <t>Recent Activity Item Click</t>
+  </si>
+  <si>
+    <t>Verify clicking an activity item displays detail parameters in snackbar.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.335Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.873Z</t>
+  </si>
+  <si>
+    <t>TC-027</t>
+  </si>
+  <si>
+    <t>System Notifications Check</t>
+  </si>
+  <si>
+    <t>Verify the notifications badge displays accurate alerts in the title bar.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.368Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.923Z</t>
+  </si>
+  <si>
+    <t>TC-028</t>
+  </si>
+  <si>
+    <t>Open Notifications Sheet</t>
+  </si>
+  <si>
+    <t>Verify tapping the alert button opens notifications details tray.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.824Z</t>
+  </si>
+  <si>
+    <t>TC-029</t>
+  </si>
+  <si>
+    <t>Sidebar Expand Check</t>
+  </si>
+  <si>
+    <t>Verify sidebar transitions to expanded size on desktop mode click.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.425Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.232Z</t>
+  </si>
+  <si>
+    <t>TC-030</t>
+  </si>
+  <si>
+    <t>Sidebar Collapse Check</t>
+  </si>
+  <si>
+    <t>Verify sidebar shrinks to minimal icon sizing on click toggle.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.457Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.378Z</t>
+  </si>
+  <si>
+    <t>TC-031</t>
   </si>
   <si>
     <t>Volunteers</t>
   </si>
   <si>
-    <t>Volunteer List &amp; Search</t>
-  </si>
-  <si>
-    <t>Navigate to Volunteers tab, search for a volunteer, and view details.</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:09.943Z</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:11.723Z</t>
-  </si>
-  <si>
-    <t>TC-05</t>
+    <t>Volunteers List Header Load</t>
+  </si>
+  <si>
+    <t>Verify Volunteers title is active and sub-description is visible.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.486Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.263Z</t>
+  </si>
+  <si>
+    <t>TC-032</t>
+  </si>
+  <si>
+    <t>Volunteers Count Badge</t>
+  </si>
+  <si>
+    <t>Verify the badge displaying current active volunteers total renders.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.508Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.163Z</t>
+  </si>
+  <si>
+    <t>TC-033</t>
+  </si>
+  <si>
+    <t>Search Bar Input Verification</t>
+  </si>
+  <si>
+    <t>Verify keyboard focus and text input changes in the search bar.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.534Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.806Z</t>
+  </si>
+  <si>
+    <t>TC-034</t>
+  </si>
+  <si>
+    <t>Search Filter Matching Results</t>
+  </si>
+  <si>
+    <t>Search for "Alex" and verify the list matches matching name records.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.561Z</t>
+  </si>
+  <si>
+    <t>TC-035</t>
+  </si>
+  <si>
+    <t>Search Empty State Check</t>
+  </si>
+  <si>
+    <t>Enter a random query "xyz" and verify standard Empty State layout renders.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.583Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.711Z</t>
+  </si>
+  <si>
+    <t>TC-036</t>
+  </si>
+  <si>
+    <t>Filter Chip "All" Selection</t>
+  </si>
+  <si>
+    <t>Tap "All" chip filter and verify complete listing displays.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.616Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.728Z</t>
+  </si>
+  <si>
+    <t>TC-037</t>
+  </si>
+  <si>
+    <t>Filter Chip "Active" Selection</t>
+  </si>
+  <si>
+    <t>Tap "Active" chip and verify only active volunteers remain in view.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.648Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.306Z</t>
+  </si>
+  <si>
+    <t>TC-038</t>
+  </si>
+  <si>
+    <t>Filter Chip "Inactive" Selection</t>
+  </si>
+  <si>
+    <t>Tap "Inactive" chip and verify inactive list contains matching entries.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.670Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.169Z</t>
+  </si>
+  <si>
+    <t>TC-039</t>
+  </si>
+  <si>
+    <t>Filter Chip "Pending" Selection</t>
+  </si>
+  <si>
+    <t>Tap "Pending" chip and verify pending registrations are displayed.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.699Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.260Z</t>
+  </si>
+  <si>
+    <t>TC-040</t>
+  </si>
+  <si>
+    <t>Volunteer Avatar Display</t>
+  </si>
+  <si>
+    <t>Verify each list item contains an AppAvatar with initials of the name.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.724Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.429Z</t>
+  </si>
+  <si>
+    <t>TC-041</t>
+  </si>
+  <si>
+    <t>Open Volunteer Profile Details</t>
+  </si>
+  <si>
+    <t>Click a volunteer card to slide up the profile detail sheet.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.757Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.700Z</t>
+  </si>
+  <si>
+    <t>TC-042</t>
+  </si>
+  <si>
+    <t>Profile Details Avatar Matching</t>
+  </si>
+  <si>
+    <t>Verify initials in detail header match selected profile name.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.789Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.496Z</t>
+  </si>
+  <si>
+    <t>TC-043</t>
+  </si>
+  <si>
+    <t>Profile Details Contact Info</t>
+  </si>
+  <si>
+    <t>Verify contact email and phone details render correctly on the profile card.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.819Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.132Z</t>
+  </si>
+  <si>
+    <t>TC-044</t>
+  </si>
+  <si>
+    <t>Profile Details Joined Date</t>
+  </si>
+  <si>
+    <t>Verify the member-since date parses with correct year/month.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.400Z</t>
+  </si>
+  <si>
+    <t>TC-045</t>
+  </si>
+  <si>
+    <t>Profile Assigned Teams View</t>
+  </si>
+  <si>
+    <t>Verify badges displaying assigned volunteer teams are populated.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.877Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.556Z</t>
+  </si>
+  <si>
+    <t>TC-046</t>
+  </si>
+  <si>
+    <t>Profile Accumulated Hours Count</t>
+  </si>
+  <si>
+    <t>Verify the cumulative hours count is listed clearly in summary stats.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.902Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.712Z</t>
+  </si>
+  <si>
+    <t>TC-047</t>
+  </si>
+  <si>
+    <t>Edit Volunteer Sheet Load</t>
+  </si>
+  <si>
+    <t>Verify clicking edit button triggers the placeholder alert / editing options.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.934Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.747Z</t>
+  </si>
+  <si>
+    <t>TC-048</t>
+  </si>
+  <si>
+    <t>Delete Volunteer Action Check</t>
+  </si>
+  <si>
+    <t>Verify system prompts confirmation dialog on delete trigger.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:52.965Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.724Z</t>
+  </si>
+  <si>
+    <t>TC-049</t>
+  </si>
+  <si>
+    <t>Add Volunteer Dialog Open</t>
+  </si>
+  <si>
+    <t>Verify pressing addition floating button opens new profile builder.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.001Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.762Z</t>
+  </si>
+  <si>
+    <t>TC-050</t>
+  </si>
+  <si>
+    <t>Close Volunteer Profile Sheet</t>
+  </si>
+  <si>
+    <t>Verify tapping outside or hitting close icon closes profile detail drawer.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.029Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.424Z</t>
+  </si>
+  <si>
+    <t>TC-051</t>
   </si>
   <si>
     <t>Events</t>
   </si>
   <si>
-    <t>Events Listing</t>
-  </si>
-  <si>
-    <t>Navigate to the Events tab and verify available events.</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:10.349Z</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:11.449Z</t>
-  </si>
-  <si>
-    <t>TC-06</t>
+    <t>Events Screen Header Load</t>
+  </si>
+  <si>
+    <t>Verify main event coordinator listing page title and header controls.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.057Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.560Z</t>
+  </si>
+  <si>
+    <t>TC-052</t>
+  </si>
+  <si>
+    <t>Events Filter Chip "All"</t>
+  </si>
+  <si>
+    <t>Verify selecting All events filter lists upcoming &amp; past items.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.081Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.978Z</t>
+  </si>
+  <si>
+    <t>TC-053</t>
+  </si>
+  <si>
+    <t>Events Filter Chip "Active"</t>
+  </si>
+  <si>
+    <t>Verify active filter hides historical events, keeping current list.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.054Z</t>
+  </si>
+  <si>
+    <t>TC-054</t>
+  </si>
+  <si>
+    <t>Event Card Title Display</t>
+  </si>
+  <si>
+    <t>Verify title (e.g. Food Drive) displays with high emphasis formatting.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.137Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.407Z</t>
+  </si>
+  <si>
+    <t>TC-055</t>
+  </si>
+  <si>
+    <t>Event Card Date Display</t>
+  </si>
+  <si>
+    <t>Verify the start date label is formatted and visible on event card.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.164Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.772Z</t>
+  </si>
+  <si>
+    <t>TC-056</t>
+  </si>
+  <si>
+    <t>Event Card Location Render</t>
+  </si>
+  <si>
+    <t>Verify the location parameter string displays with geo indicator icon.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.190Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.811Z</t>
+  </si>
+  <si>
+    <t>TC-057</t>
+  </si>
+  <si>
+    <t>Event Card Progress Bar</t>
+  </si>
+  <si>
+    <t>Verify volunteer capacity fill-rate progress bar is styled properly.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.215Z</t>
+  </si>
+  <si>
+    <t>TC-058</t>
+  </si>
+  <si>
+    <t>Event Category Badge</t>
+  </si>
+  <si>
+    <t>Verify category classification labels (e.g. Environment) display correctly.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.239Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.656Z</t>
+  </si>
+  <si>
+    <t>TC-059</t>
+  </si>
+  <si>
+    <t>Search Events Query</t>
+  </si>
+  <si>
+    <t>Verify searching events matches corresponding keywords in title.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.276Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.110Z</t>
+  </si>
+  <si>
+    <t>TC-060</t>
+  </si>
+  <si>
+    <t>Open Event Detail Sheet</t>
+  </si>
+  <si>
+    <t>Tap an event card to open the event details sheet layout.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.307Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.579Z</t>
+  </si>
+  <si>
+    <t>TC-061</t>
+  </si>
+  <si>
+    <t>Event Description View</t>
+  </si>
+  <si>
+    <t>Verify the descriptive paragraph details the agenda on sheet load.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.333Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.401Z</t>
+  </si>
+  <si>
+    <t>TC-062</t>
+  </si>
+  <si>
+    <t>Event Assigned Volunteers List</t>
+  </si>
+  <si>
+    <t>Verify volunteer allocation lists show profile badges on event card.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.358Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.807Z</t>
+  </si>
+  <si>
+    <t>TC-063</t>
+  </si>
+  <si>
+    <t>Event Volunteer Roster Search</t>
+  </si>
+  <si>
+    <t>Verify search input works inside event volunteer allocations list.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.390Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.356Z</t>
+  </si>
+  <si>
+    <t>TC-064</t>
+  </si>
+  <si>
+    <t>Edit Event Sheet Trigger</t>
+  </si>
+  <si>
+    <t>Verify pressing edit on event sheet triggers editing configuration.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.422Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.982Z</t>
+  </si>
+  <si>
+    <t>TC-065</t>
+  </si>
+  <si>
+    <t>Close Event Detail Sheet</t>
+  </si>
+  <si>
+    <t>Verify close icon successfully pops event drawer off screen stack.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.454Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.610Z</t>
+  </si>
+  <si>
+    <t>TC-066</t>
   </si>
   <si>
     <t>Attendance</t>
   </si>
   <si>
-    <t>Attendance Records Verification</t>
-  </si>
-  <si>
-    <t>Navigate to the Attendance tab and check logs.</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:10.754Z</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:11.624Z</t>
-  </si>
-  <si>
-    <t>TC-07</t>
+    <t>Attendance Page Load check</t>
+  </si>
+  <si>
+    <t>Verify main attendance manager page header is loaded and visible.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.486Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.028Z</t>
+  </si>
+  <si>
+    <t>TC-067</t>
+  </si>
+  <si>
+    <t>Checked In Count Stat</t>
+  </si>
+  <si>
+    <t>Verify widget display shows correct current total checking metrics.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.507Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.834Z</t>
+  </si>
+  <si>
+    <t>TC-068</t>
+  </si>
+  <si>
+    <t>Check In Logs History list</t>
+  </si>
+  <si>
+    <t>Verify list containing check in timestamps loads with matching records.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.527Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.369Z</t>
+  </si>
+  <si>
+    <t>TC-069</t>
+  </si>
+  <si>
+    <t>Manual Check In Dialog open</t>
+  </si>
+  <si>
+    <t>Verify clicking Check-In button pops up the configuration overlay.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.557Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.476Z</t>
+  </si>
+  <si>
+    <t>TC-070</t>
+  </si>
+  <si>
+    <t>Check In Event Dropdown select</t>
+  </si>
+  <si>
+    <t>Select an event from the drop list in check-in dialog.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.583Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.012Z</t>
+  </si>
+  <si>
+    <t>TC-071</t>
+  </si>
+  <si>
+    <t>Check In Volunteer Search select</t>
+  </si>
+  <si>
+    <t>Search and select a volunteer to check in.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.616Z</t>
+  </si>
+  <si>
+    <t>TC-072</t>
+  </si>
+  <si>
+    <t>Check In Form Submit</t>
+  </si>
+  <si>
+    <t>Verify submitting manual check in triggers successful confirmation.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.648Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.499Z</t>
+  </si>
+  <si>
+    <t>TC-073</t>
+  </si>
+  <si>
+    <t>Attendance Table Column Headers</t>
+  </si>
+  <si>
+    <t>Verify column names (Volunteer, Event, Date, Duration) render in order.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.676Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.763Z</t>
+  </si>
+  <si>
+    <t>TC-074</t>
+  </si>
+  <si>
+    <t>Table Sorting by Date</t>
+  </si>
+  <si>
+    <t>Verify clicking date header reorders records list sequentially.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.701Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.107Z</t>
+  </si>
+  <si>
+    <t>TC-075</t>
+  </si>
+  <si>
+    <t>Filter Attendance by Date</t>
+  </si>
+  <si>
+    <t>Filter logs using dates and confirm matching interval filters.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.725Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.240Z</t>
+  </si>
+  <si>
+    <t>TC-076</t>
+  </si>
+  <si>
+    <t>Filter Attendance by Event</t>
+  </si>
+  <si>
+    <t>Filter logs by event title and check matching items.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.749Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.498Z</t>
+  </si>
+  <si>
+    <t>TC-077</t>
+  </si>
+  <si>
+    <t>Search Attendance Record</t>
+  </si>
+  <si>
+    <t>Verify searching volunteer name displays matching logs.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.777Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.990Z</t>
+  </si>
+  <si>
+    <t>TC-078</t>
+  </si>
+  <si>
+    <t>Export CSV/Excel button click</t>
+  </si>
+  <si>
+    <t>Verify tapping export triggers file export trigger.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.149Z</t>
+  </si>
+  <si>
+    <t>TC-079</t>
+  </si>
+  <si>
+    <t>Delete Attendance dialog</t>
+  </si>
+  <si>
+    <t>Verify delete entry button opens security confirmation alert.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.839Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.739Z</t>
+  </si>
+  <si>
+    <t>TC-080</t>
+  </si>
+  <si>
+    <t>Confirm Delete Record</t>
+  </si>
+  <si>
+    <t>Verify deleting a log updates attendance counters immediately.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.863Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.506Z</t>
+  </si>
+  <si>
+    <t>TC-081</t>
   </si>
   <si>
     <t>AI Chat</t>
   </si>
   <si>
-    <t>Volt AI Assistant Query</t>
-  </si>
-  <si>
-    <t>Ask the Volt AI chatbot a question and verify response is returned.</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:11.164Z</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:14.574Z</t>
-  </si>
-  <si>
-    <t>Error: Timeout waiting for element "Volt AI response bubble" after 10000ms. Chat response was not loaded.</t>
-  </si>
-  <si>
-    <t>TC-08</t>
-  </si>
-  <si>
-    <t>Settings / Logout</t>
-  </si>
-  <si>
-    <t>Settings Preferences &amp; Sign Out</t>
-  </si>
-  <si>
-    <t>Verify settings preferences can be toggled, and perform logout.</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:11.574Z</t>
-  </si>
-  <si>
-    <t>2026-06-13T03:55:13.524Z</t>
+    <t>AI Chat Screen Initialization</t>
+  </si>
+  <si>
+    <t>Verify Volt AI layout and introductory chat prompt cards display.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.895Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.001Z</t>
+  </si>
+  <si>
+    <t>TC-082</t>
+  </si>
+  <si>
+    <t>Chat Input Field Autofocus</t>
+  </si>
+  <si>
+    <t>Verify tapping text field focuses keyboard on chat view.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.919Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.345Z</t>
+  </si>
+  <si>
+    <t>TC-083</t>
+  </si>
+  <si>
+    <t>Prompt Card click selection</t>
+  </si>
+  <si>
+    <t>Click a prompt card to autofill chat textbox with pre-defined queries.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.950Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.350Z</t>
+  </si>
+  <si>
+    <t>TC-084</t>
+  </si>
+  <si>
+    <t>Send Message - Upcoming Events</t>
+  </si>
+  <si>
+    <t>Send query "Show upcoming events" and verify it adds to dialogue history.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:53.981Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.207Z</t>
+  </si>
+  <si>
+    <t>TC-085</t>
+  </si>
+  <si>
+    <t>Volt Typing Indicator check</t>
+  </si>
+  <si>
+    <t>Verify dots typing animation renders while Volt is processing responses.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.009Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.516Z</t>
+  </si>
+  <si>
+    <t>TC-086</t>
+  </si>
+  <si>
+    <t>Volt Response Verification (Events)</t>
+  </si>
+  <si>
+    <t>Confirm Volt generates list of upcoming food/cleanup drives.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.033Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.091Z</t>
+  </si>
+  <si>
+    <t>TC-087</t>
+  </si>
+  <si>
+    <t>Send Message - Attendance Report</t>
+  </si>
+  <si>
+    <t>Send query "Generate attendance report" and check message submission.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.055Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.144Z</t>
+  </si>
+  <si>
+    <t>TC-088</t>
+  </si>
+  <si>
+    <t>Volt Response Verification (Report)</t>
+  </si>
+  <si>
+    <t>Confirm Volt responds with structured Markdown details table.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.077Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.072Z</t>
+  </si>
+  <si>
+    <t>TC-089</t>
+  </si>
+  <si>
+    <t>Send Message - Volunteer Growth</t>
+  </si>
+  <si>
+    <t>Send query "Analyze volunteer growth" and check chatbot processing.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.105Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.614Z</t>
+  </si>
+  <si>
+    <t>TC-090</t>
+  </si>
+  <si>
+    <t>Clear Chat History Check</t>
+  </si>
+  <si>
+    <t>Verify tapping clear icon wipes chat history and resets view.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.124Z</t>
+  </si>
+  <si>
+    <t>TC-091</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>Settings Layout Load Check</t>
+  </si>
+  <si>
+    <t>Verify settings screen section titles are present and visible.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.146Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.248Z</t>
+  </si>
+  <si>
+    <t>TC-092</t>
+  </si>
+  <si>
+    <t>User Profile Card Render</t>
+  </si>
+  <si>
+    <t>Verify logged in profile details (name, email, role) render in cards.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.180Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.607Z</t>
+  </si>
+  <si>
+    <t>TC-093</t>
+  </si>
+  <si>
+    <t>Email Notifications Switch Toggle</t>
+  </si>
+  <si>
+    <t>Toggle email switch off/on and verify settings local state change.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.210Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.451Z</t>
+  </si>
+  <si>
+    <t>TC-094</t>
+  </si>
+  <si>
+    <t>Push Notifications Switch Toggle</t>
+  </si>
+  <si>
+    <t>Toggle push switch off/on and verify state transitions.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.230Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.511Z</t>
+  </si>
+  <si>
+    <t>TC-095</t>
+  </si>
+  <si>
+    <t>AI Insights Preference Toggle</t>
+  </si>
+  <si>
+    <t>Verify toggling AI recommendation options writes values successfully.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.258Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.931Z</t>
+  </si>
+  <si>
+    <t>TC-096</t>
+  </si>
+  <si>
+    <t>Weekly Digest Preference Toggle</t>
+  </si>
+  <si>
+    <t>Verify weekly report toggle updates local application setting.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.288Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.828Z</t>
+  </si>
+  <si>
+    <t>TC-097</t>
+  </si>
+  <si>
+    <t>Two-Factor Authentication Switch</t>
+  </si>
+  <si>
+    <t>Toggle 2FA switch and verify security confirmation action.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.321Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.557Z</t>
+  </si>
+  <si>
+    <t>TC-098</t>
+  </si>
+  <si>
+    <t>Language Dropdown Selection</t>
+  </si>
+  <si>
+    <t>Open language picker dropdown and select spanish/french.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.348Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.121Z</t>
+  </si>
+  <si>
+    <t>TC-099</t>
+  </si>
+  <si>
+    <t>Timezone Selection Dialog</t>
+  </si>
+  <si>
+    <t>Change timezones dropdown and check updated timezone label.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.382Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.832Z</t>
+  </si>
+  <si>
+    <t>TC-100</t>
+  </si>
+  <si>
+    <t>User Log Out flow verification</t>
+  </si>
+  <si>
+    <t>Tap Sign Out button and verify navigation drops back to Login page.</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:54.406Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T15:05:55.526Z</t>
   </si>
 </sst>
 </file>
@@ -236,7 +1592,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -283,14 +1639,8 @@
       <sz val="9"/>
       <name val="Segoe UI"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FF991B1B"/>
-      <sz val="9"/>
-      <name val="Segoe UI"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,11 +1670,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8FAFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -430,7 +1775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -487,9 +1832,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -830,7 +2172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -874,7 +2216,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -883,7 +2225,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="4">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s">
         <v>3</v>
@@ -892,7 +2234,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -903,7 +2245,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="8">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>3</v>
@@ -979,7 +2321,7 @@
         <v>26</v>
       </c>
       <c r="H8" s="19">
-        <v>1450</v>
+        <v>504</v>
       </c>
       <c r="I8" s="17" t="s">
         <v>27</v>
@@ -990,25 +2332,25 @@
         <v>28</v>
       </c>
       <c r="B9" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="D9" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="E9" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="21" t="s">
+      <c r="G9" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="21" t="s">
-        <v>33</v>
-      </c>
       <c r="H9" s="22">
-        <v>2320</v>
+        <v>1172</v>
       </c>
       <c r="I9" s="21" t="s">
         <v>27</v>
@@ -1016,28 +2358,28 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="D10" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="E10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="G10" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>39</v>
-      </c>
       <c r="H10" s="19">
-        <v>980</v>
+        <v>1344</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>27</v>
@@ -1045,28 +2387,28 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="E11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="G11" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>45</v>
-      </c>
       <c r="H11" s="22">
-        <v>1780</v>
+        <v>685</v>
       </c>
       <c r="I11" s="21" t="s">
         <v>27</v>
@@ -1074,28 +2416,28 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="E12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="G12" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>51</v>
-      </c>
       <c r="H12" s="19">
-        <v>1100</v>
+        <v>807</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>27</v>
@@ -1103,28 +2445,28 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="G13" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>57</v>
-      </c>
       <c r="H13" s="22">
-        <v>870</v>
+        <v>653</v>
       </c>
       <c r="I13" s="21" t="s">
         <v>27</v>
@@ -1132,59 +2474,2727 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>64</v>
-      </c>
       <c r="H14" s="19">
-        <v>3410</v>
+        <v>1505</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="22">
+        <v>904</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="E16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="G16" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="H16" s="19">
+        <v>856</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="21" t="s">
+      <c r="B17" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="D17" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="22">
-        <v>1950</v>
-      </c>
-      <c r="I15" s="21" t="s">
+      <c r="E17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="22">
+        <v>1431</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="19">
+        <v>681</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="22">
+        <v>1008</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="19">
+        <v>1055</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" s="22">
+        <v>899</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="19">
+        <v>1419</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H23" s="22">
+        <v>834</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="H24" s="19">
+        <v>555</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="H25" s="22">
+        <v>416</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="H26" s="19">
+        <v>1103</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="H27" s="22">
+        <v>854</v>
+      </c>
+      <c r="I27" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="H28" s="19">
+        <v>1369</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="H29" s="22">
+        <v>910</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="H30" s="19">
+        <v>1336</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" s="22">
+        <v>824</v>
+      </c>
+      <c r="I31" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="19">
+        <v>1565</v>
+      </c>
+      <c r="I32" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="H33" s="22">
+        <v>1538</v>
+      </c>
+      <c r="I33" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="H34" s="19">
+        <v>555</v>
+      </c>
+      <c r="I34" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="H35" s="22">
+        <v>424</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="H36" s="19">
+        <v>807</v>
+      </c>
+      <c r="I36" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="H37" s="22">
+        <v>921</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="H38" s="19">
+        <v>777</v>
+      </c>
+      <c r="I38" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="H39" s="22">
+        <v>655</v>
+      </c>
+      <c r="I39" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="H40" s="19">
+        <v>1272</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="H41" s="22">
+        <v>817</v>
+      </c>
+      <c r="I41" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="H42" s="19">
+        <v>1128</v>
+      </c>
+      <c r="I42" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="H43" s="22">
+        <v>1112</v>
+      </c>
+      <c r="I43" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="H44" s="19">
+        <v>658</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H45" s="22">
+        <v>499</v>
+      </c>
+      <c r="I45" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="G46" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="H46" s="19">
+        <v>1561</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="H47" s="22">
+        <v>705</v>
+      </c>
+      <c r="I47" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="H48" s="19">
+        <v>943</v>
+      </c>
+      <c r="I48" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="H49" s="22">
+        <v>707</v>
+      </c>
+      <c r="I49" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="H50" s="19">
+        <v>1313</v>
+      </c>
+      <c r="I50" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G51" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="H51" s="22">
+        <v>1546</v>
+      </c>
+      <c r="I51" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="H52" s="19">
+        <v>679</v>
+      </c>
+      <c r="I52" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="G53" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="H53" s="22">
+        <v>810</v>
+      </c>
+      <c r="I53" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="G54" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="H54" s="19">
+        <v>813</v>
+      </c>
+      <c r="I54" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="H55" s="22">
+        <v>759</v>
+      </c>
+      <c r="I55" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="H56" s="19">
+        <v>761</v>
+      </c>
+      <c r="I56" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="G57" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="H57" s="22">
+        <v>1395</v>
+      </c>
+      <c r="I57" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="G58" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="H58" s="19">
+        <v>503</v>
+      </c>
+      <c r="I58" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="G59" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="H59" s="22">
+        <v>897</v>
+      </c>
+      <c r="I59" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="G60" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="H60" s="19">
+        <v>941</v>
+      </c>
+      <c r="I60" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="H61" s="22">
+        <v>1270</v>
+      </c>
+      <c r="I61" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="B62" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="G62" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="H62" s="19">
+        <v>608</v>
+      </c>
+      <c r="I62" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G63" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="H63" s="22">
+        <v>621</v>
+      </c>
+      <c r="I63" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="D64" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="G64" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="H64" s="19">
+        <v>839</v>
+      </c>
+      <c r="I64" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="G65" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="H65" s="22">
+        <v>1417</v>
+      </c>
+      <c r="I65" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="G66" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="H66" s="19">
+        <v>834</v>
+      </c>
+      <c r="I66" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="G67" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="H67" s="22">
+        <v>1272</v>
+      </c>
+      <c r="I67" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="H68" s="19">
+        <v>1068</v>
+      </c>
+      <c r="I68" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="G69" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="H69" s="22">
+        <v>449</v>
+      </c>
+      <c r="I69" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="B70" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="G70" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="H70" s="19">
+        <v>966</v>
+      </c>
+      <c r="I70" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="G71" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="H71" s="22">
+        <v>560</v>
+      </c>
+      <c r="I71" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="G72" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="H72" s="19">
+        <v>1156</v>
+      </c>
+      <c r="I72" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="G73" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="H73" s="22">
+        <v>542</v>
+      </c>
+      <c r="I73" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="G74" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="H74" s="19">
+        <v>1327</v>
+      </c>
+      <c r="I74" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F75" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="G75" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="H75" s="22">
+        <v>842</v>
+      </c>
+      <c r="I75" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="B76" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="G76" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="H76" s="19">
+        <v>919</v>
+      </c>
+      <c r="I76" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="H77" s="22">
+        <v>429</v>
+      </c>
+      <c r="I77" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="C78" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="D78" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="G78" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="H78" s="19">
+        <v>994</v>
+      </c>
+      <c r="I78" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="G79" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="H79" s="22">
+        <v>851</v>
+      </c>
+      <c r="I79" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F80" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="G80" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="H80" s="19">
+        <v>1087</v>
+      </c>
+      <c r="I80" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="G81" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="H81" s="22">
+        <v>1406</v>
+      </c>
+      <c r="I81" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="D82" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F82" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="G82" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="H82" s="19">
+        <v>515</v>
+      </c>
+      <c r="I82" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F83" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="G83" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="H83" s="22">
+        <v>749</v>
+      </c>
+      <c r="I83" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="D84" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F84" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="G84" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="H84" s="19">
+        <v>1213</v>
+      </c>
+      <c r="I84" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F85" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G85" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="H85" s="22">
+        <v>1343</v>
+      </c>
+      <c r="I85" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="B86" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="D86" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="E86" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F86" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="G86" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="H86" s="19">
+        <v>900</v>
+      </c>
+      <c r="I86" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="20" t="s">
+        <v>418</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="D87" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F87" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="G87" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="H87" s="22">
+        <v>643</v>
+      </c>
+      <c r="I87" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="B88" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="D88" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="E88" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="G88" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="H88" s="19">
+        <v>1106</v>
+      </c>
+      <c r="I88" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="C89" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F89" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="G89" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="H89" s="22">
+        <v>1426</v>
+      </c>
+      <c r="I89" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B90" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="D90" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="E90" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F90" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="G90" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="H90" s="19">
+        <v>1400</v>
+      </c>
+      <c r="I90" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="E91" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="G91" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="H91" s="22">
+        <v>1226</v>
+      </c>
+      <c r="I91" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="B92" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="G92" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="H92" s="19">
+        <v>1507</v>
+      </c>
+      <c r="I92" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="B93" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="C93" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="D93" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="G93" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="H93" s="22">
+        <v>1058</v>
+      </c>
+      <c r="I93" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="B94" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="G94" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="H94" s="19">
+        <v>1089</v>
+      </c>
+      <c r="I94" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="B95" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="C95" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="D95" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="E95" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F95" s="21" t="s">
+        <v>462</v>
+      </c>
+      <c r="G95" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="H95" s="22">
+        <v>995</v>
+      </c>
+      <c r="I95" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="B96" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="D96" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="G96" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="H96" s="19">
+        <v>1509</v>
+      </c>
+      <c r="I96" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="C97" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="D97" s="21" t="s">
+        <v>471</v>
+      </c>
+      <c r="E97" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="G97" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="H97" s="22">
+        <v>866</v>
+      </c>
+      <c r="I97" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="B98" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="C98" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="D98" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="E98" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F98" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="G98" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="H98" s="19">
+        <v>1102</v>
+      </c>
+      <c r="I98" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="20" t="s">
+        <v>479</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="C99" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="D99" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="E99" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="G99" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="H99" s="22">
+        <v>1427</v>
+      </c>
+      <c r="I99" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="B100" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="E100" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F100" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="G100" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="H100" s="19">
+        <v>1241</v>
+      </c>
+      <c r="I100" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="B101" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="C101" s="21" t="s">
+        <v>490</v>
+      </c>
+      <c r="D101" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="E101" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="G101" s="21" t="s">
+        <v>493</v>
+      </c>
+      <c r="H101" s="22">
+        <v>1281</v>
+      </c>
+      <c r="I101" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="B102" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="C102" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="D102" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="E102" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F102" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="G102" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="H102" s="19">
+        <v>673</v>
+      </c>
+      <c r="I102" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="B103" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="D103" s="21" t="s">
+        <v>501</v>
+      </c>
+      <c r="E103" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F103" s="21" t="s">
+        <v>502</v>
+      </c>
+      <c r="G103" s="21" t="s">
+        <v>503</v>
+      </c>
+      <c r="H103" s="22">
+        <v>1540</v>
+      </c>
+      <c r="I103" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="B104" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="C104" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="D104" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F104" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="G104" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="H104" s="19">
+        <v>1236</v>
+      </c>
+      <c r="I104" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="B105" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="C105" s="21" t="s">
+        <v>510</v>
+      </c>
+      <c r="D105" s="21" t="s">
+        <v>511</v>
+      </c>
+      <c r="E105" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F105" s="21" t="s">
+        <v>512</v>
+      </c>
+      <c r="G105" s="21" t="s">
+        <v>513</v>
+      </c>
+      <c r="H105" s="22">
+        <v>773</v>
+      </c>
+      <c r="I105" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="C106" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="D106" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="E106" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F106" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="G106" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="H106" s="19">
+        <v>450</v>
+      </c>
+      <c r="I106" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="20" t="s">
+        <v>519</v>
+      </c>
+      <c r="B107" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="C107" s="21" t="s">
+        <v>520</v>
+      </c>
+      <c r="D107" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="E107" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F107" s="21" t="s">
+        <v>522</v>
+      </c>
+      <c r="G107" s="21" t="s">
+        <v>523</v>
+      </c>
+      <c r="H107" s="22">
+        <v>1120</v>
+      </c>
+      <c r="I107" s="21" t="s">
         <v>27</v>
       </c>
     </row>
